--- a/datalog.xlsx
+++ b/datalog.xlsx
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AD8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -668,6 +668,9 @@
       <c r="AC1" t="str">
         <v>Sit_Vid fritidsaktivitet</v>
       </c>
+      <c r="AD1" t="str">
+        <v>Liksidig_HNS</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -757,6 +760,9 @@
       <c r="AC2" t="str">
         <v>Aldrig</v>
       </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -846,6 +852,9 @@
       <c r="AC3" t="str">
         <v>Aldrig</v>
       </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -935,6 +944,9 @@
       <c r="AC4" t="str">
         <v>Ibland</v>
       </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1024,6 +1036,9 @@
       <c r="AC5" t="str">
         <v>Aldrig</v>
       </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1113,10 +1128,197 @@
       <c r="AC6" t="str">
         <v>Sällan</v>
       </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>77</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C7" t="str">
+        <v>7-18</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2013</v>
+      </c>
+      <c r="E7" t="str">
+        <v>5.00</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>5.00</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Grav (71-80 dB)</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Grav (71-80 dB)</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Ledningshinder</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Ledningshinder</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Bakom örat</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Baha</v>
+      </c>
+      <c r="T7" t="str">
+        <v>Sällan</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="V7" t="str">
+        <v>Alltid</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>Sällan</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>Sällan</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>Sällan</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>Ja</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>hello</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>7-18</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2012</v>
+      </c>
+      <c r="E8" t="str">
+        <v>99.00</v>
+      </c>
+      <c r="F8" t="str">
+        <v>77.00</v>
+      </c>
+      <c r="G8" t="str">
+        <v>77.00</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Måttlig (41-60 dB)</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Måttlig (41-60 dB)</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Sensorineural</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Sensorineural</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Bakom örat</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Bakom örat</v>
+      </c>
+      <c r="T8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="V8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>Ja</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datalog.xlsx
+++ b/datalog.xlsx
@@ -578,7 +578,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AC6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -668,9 +668,6 @@
       <c r="AC1" t="str">
         <v>Sit_Vid fritidsaktivitet</v>
       </c>
-      <c r="AD1" t="str">
-        <v>Liksidig_HNS</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -760,9 +757,6 @@
       <c r="AC2" t="str">
         <v>Aldrig</v>
       </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -852,9 +846,6 @@
       <c r="AC3" t="str">
         <v>Aldrig</v>
       </c>
-      <c r="AD3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -944,9 +935,6 @@
       <c r="AC4" t="str">
         <v>Ibland</v>
       </c>
-      <c r="AD4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1036,9 +1024,6 @@
       <c r="AC5" t="str">
         <v>Aldrig</v>
       </c>
-      <c r="AD5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1128,197 +1113,10 @@
       <c r="AC6" t="str">
         <v>Sällan</v>
       </c>
-      <c r="AD6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>77</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C7" t="str">
-        <v>7-18</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2013</v>
-      </c>
-      <c r="E7" t="str">
-        <v>5.00</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>5.00</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Grav (71-80 dB)</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Grav (71-80 dB)</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Ledningshinder</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Ledningshinder</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Ja</v>
-      </c>
-      <c r="M7" t="str">
-        <v>Ja</v>
-      </c>
-      <c r="N7" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="R7" t="str">
-        <v>Bakom örat</v>
-      </c>
-      <c r="S7" t="str">
-        <v>Baha</v>
-      </c>
-      <c r="T7" t="str">
-        <v>Sällan</v>
-      </c>
-      <c r="U7" t="str">
-        <v>Ibland</v>
-      </c>
-      <c r="V7" t="str">
-        <v>Alltid</v>
-      </c>
-      <c r="W7" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="X7" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="Y7" t="str">
-        <v>Sällan</v>
-      </c>
-      <c r="Z7" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AB7" t="str">
-        <v>Sällan</v>
-      </c>
-      <c r="AC7" t="str">
-        <v>Sällan</v>
-      </c>
-      <c r="AD7" t="str">
-        <v>Ja</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>hello</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>7-18</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2012</v>
-      </c>
-      <c r="E8" t="str">
-        <v>99.00</v>
-      </c>
-      <c r="F8" t="str">
-        <v>77.00</v>
-      </c>
-      <c r="G8" t="str">
-        <v>77.00</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Måttlig (41-60 dB)</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Måttlig (41-60 dB)</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Sensorineural</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Sensorineural</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="M8" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Ja</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Ja</v>
-      </c>
-      <c r="P8" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Nej</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Bakom örat</v>
-      </c>
-      <c r="S8" t="str">
-        <v>Bakom örat</v>
-      </c>
-      <c r="T8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="U8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="V8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="W8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="X8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="Y8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="Z8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AC8" t="str">
-        <v>Aldrig</v>
-      </c>
-      <c r="AD8" t="str">
-        <v>Ja</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datalog.xlsx
+++ b/datalog.xlsx
@@ -1,129 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\withe\.gemini\antigravity\scratch\DatalogHA\datalog-ha\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE100C5-FDE7-46A6-9C75-FD9353A67098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="0-6" sheetId="1" r:id="rId1"/>
     <sheet name="7-18" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
-  <si>
-    <t>PatientID</t>
-  </si>
-  <si>
-    <t>Datum</t>
-  </si>
-  <si>
-    <t>Åldersgrupp</t>
-  </si>
-  <si>
-    <t>Födelseår</t>
-  </si>
-  <si>
-    <t>Time_Right</t>
-  </si>
-  <si>
-    <t>Est_Time_L</t>
-  </si>
-  <si>
-    <t>Est_Time_R</t>
-  </si>
-  <si>
-    <t>HNS_Grade_L</t>
-  </si>
-  <si>
-    <t>HNS_Grade_R</t>
-  </si>
-  <si>
-    <t>HNS_Type_L</t>
-  </si>
-  <si>
-    <t>HNS_Type_R</t>
-  </si>
-  <si>
-    <t>Basnedsattning_L</t>
-  </si>
-  <si>
-    <t>Basnedsattning_R</t>
-  </si>
-  <si>
-    <t>Diskantnedsattning_L</t>
-  </si>
-  <si>
-    <t>Diskantnedsattning_R</t>
-  </si>
-  <si>
-    <t>FlatLoss_L</t>
-  </si>
-  <si>
-    <t>FlatLoss_R</t>
-  </si>
-  <si>
-    <t>HA_Type_L</t>
-  </si>
-  <si>
-    <t>HA_Type_R</t>
-  </si>
-  <si>
-    <t>Sit_Vid måltid</t>
-  </si>
-  <si>
-    <t>Sit_Egen lek</t>
-  </si>
-  <si>
-    <t>Sit_Lek/aktivitet med föräldrar/kompisar</t>
-  </si>
-  <si>
-    <t>Sit_TV/dator/surfplatta</t>
-  </si>
-  <si>
-    <t>Sit_Vid läggdags</t>
-  </si>
-  <si>
-    <t>Sit_I barnvagnen</t>
-  </si>
-  <si>
-    <t>Sit_I bilen</t>
-  </si>
-  <si>
-    <t>Sit_På förskolan</t>
-  </si>
-  <si>
-    <t>Sit_Utomhus</t>
-  </si>
-  <si>
-    <t>Sit_På offentliga platser</t>
-  </si>
-  <si>
-    <t>Sit_Egen aktivitet tex ensam hemma</t>
-  </si>
-  <si>
-    <t>Sit_I skolan</t>
-  </si>
-  <si>
-    <t>Sit_Vid fritidsaktivitet</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -153,21 +66,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -492,211 +397,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>28</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PatientID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Datum</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Åldersgrupp</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Födelseår</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Time_Right</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Est_Time_L</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Est_Time_R</v>
+      </c>
+      <c r="H1" t="str">
+        <v>HNS_Grade_L</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HNS_Grade_R</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HNS_Type_L</v>
+      </c>
+      <c r="K1" t="str">
+        <v>HNS_Type_R</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Basnedsattning_L</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Basnedsattning_R</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Diskantnedsattning_L</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Diskantnedsattning_R</v>
+      </c>
+      <c r="P1" t="str">
+        <v>FlatLoss_L</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>FlatLoss_R</v>
+      </c>
+      <c r="R1" t="str">
+        <v>HA_Type_L</v>
+      </c>
+      <c r="S1" t="str">
+        <v>HA_Type_R</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Sit_Vid måltid</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Sit_Egen lek</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Sit_Lek/aktivitet med föräldrar/kompisar</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Sit_TV/dator/surfplatta</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Sit_Vid läggdags</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Sit_I barnvagnen</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Sit_I bilen</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Sit_På förskolan</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Sit_Utomhus</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>Sit_På offentliga platser</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AD2"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>PatientID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Datum</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Åldersgrupp</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Födelseår</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Time_Right</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Est_Time_L</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Est_Time_R</v>
+      </c>
+      <c r="H1" t="str">
+        <v>HNS_Grade_L</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HNS_Grade_R</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HNS_Type_L</v>
+      </c>
+      <c r="K1" t="str">
+        <v>HNS_Type_R</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Liksidig_HNS</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Basnedsattning_L</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Basnedsattning_R</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Diskantnedsattning_L</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Diskantnedsattning_R</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>FlatLoss_L</v>
+      </c>
+      <c r="R1" t="str">
+        <v>FlatLoss_R</v>
+      </c>
+      <c r="S1" t="str">
+        <v>HA_Type_L</v>
+      </c>
+      <c r="T1" t="str">
+        <v>HA_Type_R</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Sit_Vid måltid</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Sit_Egen aktivitet tex ensam hemma</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Sit_Lek/aktivitet med föräldrar/kompisar</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Sit_TV/dator/surfplatta</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Sit_Vid läggdags</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Sit_I bilen</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Sit_I skolan</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Sit_På offentliga platser</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>Sit_Utomhus</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>Sit_Vid fritidsaktivitet</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>31</v>
+      <c r="B2" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C2" t="str">
+        <v>7-18</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2018</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2.22</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Normal (&lt;20)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Måttlig (41-60 dB)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>---</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Ledningshinder</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>Baha</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Sällan</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Alltid</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Ibland</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:29" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AC1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datalog.xlsx
+++ b/datalog.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,64 +435,158 @@
         <v>HNS_Type_R</v>
       </c>
       <c r="L1" t="str">
+        <v>Liksidig_HNS</v>
+      </c>
+      <c r="M1" t="str">
         <v>Basnedsattning_L</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Basnedsattning_R</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Diskantnedsattning_L</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Diskantnedsattning_R</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>FlatLoss_L</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>FlatLoss_R</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>HA_Type_L</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>HA_Type_R</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>Sit_Vid måltid</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>Sit_Egen lek</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>Sit_Lek/aktivitet med föräldrar/kompisar</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>Sit_TV/dator/surfplatta</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Y1" t="str">
         <v>Sit_Vid läggdags</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>Sit_I barnvagnen</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>Sit_I bilen</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AB1" t="str">
         <v>Sit_På förskolan</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AC1" t="str">
         <v>Sit_Utomhus</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AD1" t="str">
         <v>Sit_På offentliga platser</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="C2" t="str">
+        <v>0-6</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2024</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>0.08</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Normal (&lt;20)</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Lätt (26-40 dB)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>---</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Ledningshinder</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Ja</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Nej</v>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v>Baha</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Ibland</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Aldrig</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Aldrig</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD2"/>
   </ignoredErrors>
 </worksheet>
 </file>
